--- a/reports/tables/first_visit_model_tiers.xlsx
+++ b/reports/tables/first_visit_model_tiers.xlsx
@@ -482,28 +482,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>396</v>
+        <v>296</v>
       </c>
       <c r="C2" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0371</v>
+        <v>0.0158</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0579</v>
+        <v>0.0417</v>
       </c>
       <c r="G2" t="n">
-        <v>246</v>
+        <v>185</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05303030303030303</v>
+        <v>0.03378378378378379</v>
       </c>
       <c r="I2" t="n">
-        <v>5.3</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="3">
@@ -513,28 +513,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>201</v>
+        <v>301</v>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="D3" t="n">
-        <v>0.134</v>
+        <v>0.0987</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0633</v>
+        <v>0.0424</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="G3" t="n">
-        <v>127</v>
+        <v>194</v>
       </c>
       <c r="H3" t="n">
-        <v>0.09950248756218906</v>
+        <v>0.1029900332225914</v>
       </c>
       <c r="I3" t="n">
-        <v>10</v>
+        <v>10.3</v>
       </c>
     </row>
   </sheetData>
